--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Wikström, Tyr Nilsson, Marie Persson</t>
+          <t>Petra Wikström, Marie Persson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Wikström, Marie Persson, Tyr Nilsson</t>
+          <t>Petra Wikström, Tyr Nilsson, Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY202"/>
+  <dimension ref="A1:AY203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22446,10 +22446,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135325194</v>
+        <v>135513308</v>
       </c>
       <c r="B196" t="n">
-        <v>99217</v>
+        <v>98063</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22457,37 +22457,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>634687</v>
+        <v>634820</v>
       </c>
       <c r="R196" t="n">
-        <v>7292665</v>
+        <v>7292749</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22541,23 +22541,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
-        </is>
-      </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135325198</v>
+        <v>135325194</v>
       </c>
       <c r="B197" t="n">
         <v>99217</v>
@@ -22592,13 +22588,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>634768</v>
+        <v>634687</v>
       </c>
       <c r="R197" t="n">
-        <v>7292709</v>
+        <v>7292665</v>
       </c>
       <c r="S197" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22627,7 +22623,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22637,7 +22633,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22668,7 +22664,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135325206</v>
+        <v>135325198</v>
       </c>
       <c r="B198" t="n">
         <v>99217</v>
@@ -22703,13 +22699,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>634867</v>
+        <v>634768</v>
       </c>
       <c r="R198" t="n">
-        <v>7292703</v>
+        <v>7292709</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22738,7 +22734,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22748,7 +22744,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22779,7 +22775,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135325207</v>
+        <v>135325206</v>
       </c>
       <c r="B199" t="n">
         <v>99217</v>
@@ -22814,10 +22810,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>634875</v>
+        <v>634867</v>
       </c>
       <c r="R199" t="n">
-        <v>7292695</v>
+        <v>7292703</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22849,7 +22845,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22859,7 +22855,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22890,7 +22886,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135325249</v>
+        <v>135325207</v>
       </c>
       <c r="B200" t="n">
         <v>99217</v>
@@ -22925,10 +22921,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634995</v>
+        <v>634875</v>
       </c>
       <c r="R200" t="n">
-        <v>7292655</v>
+        <v>7292695</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22960,7 +22956,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22970,7 +22966,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23001,7 +22997,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135325253</v>
+        <v>135325249</v>
       </c>
       <c r="B201" t="n">
         <v>99217</v>
@@ -23036,10 +23032,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634917</v>
+        <v>634995</v>
       </c>
       <c r="R201" t="n">
-        <v>7292715</v>
+        <v>7292655</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23071,7 +23067,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -23081,7 +23077,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23112,7 +23108,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135325254</v>
+        <v>135325253</v>
       </c>
       <c r="B202" t="n">
         <v>99217</v>
@@ -23147,10 +23143,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>634872</v>
+        <v>634917</v>
       </c>
       <c r="R202" t="n">
-        <v>7292742</v>
+        <v>7292715</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23182,7 +23178,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23192,7 +23188,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23216,6 +23212,117 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>135325254</v>
+      </c>
+      <c r="B203" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>634872</v>
+      </c>
+      <c r="R203" t="n">
+        <v>7292742</v>
+      </c>
+      <c r="S203" t="n">
+        <v>5</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Fransén</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY203"/>
+  <dimension ref="A1:AY204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21330,47 +21330,42 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>135250794</v>
+        <v>135513446</v>
       </c>
       <c r="B186" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Maddávrrie, Maddávrrie, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>634837</v>
+        <v>634713</v>
       </c>
       <c r="R186" t="n">
         <v>7292779</v>
@@ -21400,17 +21395,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gran.</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21425,19 +21425,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>135331406</v>
+        <v>135250794</v>
       </c>
       <c r="B187" t="n">
         <v>57975</v>
@@ -21473,17 +21473,17 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Maskaure maddagielas s, Pi lm</t>
+          <t>Maddávrrie, Maddávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>634875</v>
+        <v>634837</v>
       </c>
       <c r="R187" t="n">
-        <v>7292694</v>
+        <v>7292779</v>
       </c>
       <c r="S187" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21507,27 +21507,17 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack i gran.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21542,26 +21532,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY187" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>135325213</v>
+        <v>135331406</v>
       </c>
       <c r="B188" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21569,37 +21555,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Maskaure maddagielas s, Pi lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>634950</v>
+        <v>634875</v>
       </c>
       <c r="R188" t="n">
-        <v>7292624</v>
+        <v>7292694</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21628,7 +21619,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -21638,7 +21629,12 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21653,12 +21649,12 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -21669,32 +21665,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>135325195</v>
+        <v>135325213</v>
       </c>
       <c r="B189" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21704,10 +21700,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>634716</v>
+        <v>634950</v>
       </c>
       <c r="R189" t="n">
-        <v>7292691</v>
+        <v>7292624</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21739,7 +21735,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21749,7 +21745,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21780,10 +21776,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>135325197</v>
+        <v>135325195</v>
       </c>
       <c r="B190" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21791,21 +21787,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21815,10 +21811,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>634757</v>
+        <v>634716</v>
       </c>
       <c r="R190" t="n">
-        <v>7292709</v>
+        <v>7292691</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21850,7 +21846,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21860,7 +21856,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21891,7 +21887,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135325201</v>
+        <v>135325197</v>
       </c>
       <c r="B191" t="n">
         <v>99099</v>
@@ -21926,13 +21922,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>634821</v>
+        <v>634757</v>
       </c>
       <c r="R191" t="n">
-        <v>7292707</v>
+        <v>7292709</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21961,7 +21957,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21971,7 +21967,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22002,7 +21998,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135325255</v>
+        <v>135325201</v>
       </c>
       <c r="B192" t="n">
         <v>99099</v>
@@ -22037,13 +22033,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>634849</v>
+        <v>634821</v>
       </c>
       <c r="R192" t="n">
-        <v>7292752</v>
+        <v>7292707</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22072,7 +22068,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22082,7 +22078,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22113,10 +22109,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>135325217</v>
+        <v>135325255</v>
       </c>
       <c r="B193" t="n">
-        <v>106309</v>
+        <v>99099</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22124,21 +22120,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22148,13 +22144,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>634990</v>
+        <v>634849</v>
       </c>
       <c r="R193" t="n">
-        <v>7292586</v>
+        <v>7292752</v>
       </c>
       <c r="S193" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22183,7 +22179,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22193,7 +22189,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22224,10 +22220,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135325216</v>
+        <v>135325217</v>
       </c>
       <c r="B194" t="n">
-        <v>98066</v>
+        <v>106309</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22235,21 +22231,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22259,13 +22255,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>634997</v>
+        <v>634990</v>
       </c>
       <c r="R194" t="n">
-        <v>7292604</v>
+        <v>7292586</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22294,7 +22290,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22304,7 +22300,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22335,10 +22331,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135325203</v>
+        <v>135325216</v>
       </c>
       <c r="B195" t="n">
-        <v>98060</v>
+        <v>98066</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22346,16 +22342,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -22370,13 +22366,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>634855</v>
+        <v>634997</v>
       </c>
       <c r="R195" t="n">
-        <v>7292707</v>
+        <v>7292604</v>
       </c>
       <c r="S195" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22405,7 +22401,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22415,7 +22411,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22446,10 +22442,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135513308</v>
+        <v>135325203</v>
       </c>
       <c r="B196" t="n">
-        <v>98063</v>
+        <v>98060</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22457,16 +22453,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -22477,17 +22473,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>634820</v>
+        <v>634855</v>
       </c>
       <c r="R196" t="n">
-        <v>7292749</v>
+        <v>7292707</v>
       </c>
       <c r="S196" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22516,7 +22512,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22526,7 +22522,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22541,22 +22537,26 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY196" t="inlineStr"/>
+          <t>Pia Edfors, Sofia Fransén</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135325194</v>
+        <v>135513308</v>
       </c>
       <c r="B197" t="n">
-        <v>99217</v>
+        <v>98063</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22564,37 +22564,37 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>634687</v>
+        <v>634820</v>
       </c>
       <c r="R197" t="n">
-        <v>7292665</v>
+        <v>7292749</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22648,23 +22648,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
-        </is>
-      </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135325198</v>
+        <v>135325194</v>
       </c>
       <c r="B198" t="n">
         <v>99217</v>
@@ -22699,13 +22695,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>634768</v>
+        <v>634687</v>
       </c>
       <c r="R198" t="n">
-        <v>7292709</v>
+        <v>7292665</v>
       </c>
       <c r="S198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22734,7 +22730,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22744,7 +22740,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22775,7 +22771,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135325206</v>
+        <v>135325198</v>
       </c>
       <c r="B199" t="n">
         <v>99217</v>
@@ -22810,13 +22806,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>634867</v>
+        <v>634768</v>
       </c>
       <c r="R199" t="n">
-        <v>7292703</v>
+        <v>7292709</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22845,7 +22841,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22855,7 +22851,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22886,7 +22882,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135325207</v>
+        <v>135325206</v>
       </c>
       <c r="B200" t="n">
         <v>99217</v>
@@ -22921,10 +22917,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634875</v>
+        <v>634867</v>
       </c>
       <c r="R200" t="n">
-        <v>7292695</v>
+        <v>7292703</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22956,7 +22952,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22966,7 +22962,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22997,7 +22993,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135325249</v>
+        <v>135325207</v>
       </c>
       <c r="B201" t="n">
         <v>99217</v>
@@ -23032,10 +23028,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634995</v>
+        <v>634875</v>
       </c>
       <c r="R201" t="n">
-        <v>7292655</v>
+        <v>7292695</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23067,7 +23063,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -23077,7 +23073,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23108,7 +23104,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135325253</v>
+        <v>135325249</v>
       </c>
       <c r="B202" t="n">
         <v>99217</v>
@@ -23143,10 +23139,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>634917</v>
+        <v>634995</v>
       </c>
       <c r="R202" t="n">
-        <v>7292715</v>
+        <v>7292655</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23178,7 +23174,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23188,7 +23184,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23219,7 +23215,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135325254</v>
+        <v>135325253</v>
       </c>
       <c r="B203" t="n">
         <v>99217</v>
@@ -23254,10 +23250,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>634872</v>
+        <v>634917</v>
       </c>
       <c r="R203" t="n">
-        <v>7292742</v>
+        <v>7292715</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23289,7 +23285,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23299,7 +23295,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23323,6 +23319,117 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>135325254</v>
+      </c>
+      <c r="B204" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>634872</v>
+      </c>
+      <c r="R204" t="n">
+        <v>7292742</v>
+      </c>
+      <c r="S204" t="n">
+        <v>5</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Fransén</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -16810,10 +16810,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135325219</v>
+        <v>135513719</v>
       </c>
       <c r="B146" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16821,34 +16821,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>634989</v>
+        <v>634994</v>
       </c>
       <c r="R146" t="n">
-        <v>7292576</v>
+        <v>7292513</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16905,48 +16905,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135325234</v>
+        <v>135325219</v>
       </c>
       <c r="B147" t="n">
-        <v>78377</v>
+        <v>80500</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16956,10 +16952,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>634815</v>
+        <v>634989</v>
       </c>
       <c r="R147" t="n">
-        <v>7292218</v>
+        <v>7292576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16991,7 +16987,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17001,7 +16997,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17032,10 +17028,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135325223</v>
+        <v>135325234</v>
       </c>
       <c r="B148" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17043,21 +17039,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17067,10 +17063,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>634971</v>
+        <v>634815</v>
       </c>
       <c r="R148" t="n">
-        <v>7292487</v>
+        <v>7292218</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17102,7 +17098,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17112,12 +17108,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Färska födosöksspår</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17148,7 +17139,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135331408</v>
+        <v>135325223</v>
       </c>
       <c r="B149" t="n">
         <v>57975</v>
@@ -17177,24 +17168,19 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Maskaure maddagielas s, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>635125</v>
+        <v>634971</v>
       </c>
       <c r="R149" t="n">
-        <v>7292371</v>
+        <v>7292487</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17223,7 +17209,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17233,12 +17219,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Färska födosöksspår</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17253,12 +17239,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17269,7 +17255,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135331435</v>
+        <v>135331408</v>
       </c>
       <c r="B150" t="n">
         <v>57975</v>
@@ -17300,7 +17286,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -17309,13 +17295,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>635186</v>
+        <v>635125</v>
       </c>
       <c r="R150" t="n">
-        <v>7292228</v>
+        <v>7292371</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17344,7 +17330,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17354,12 +17340,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17390,7 +17376,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135331436</v>
+        <v>135331435</v>
       </c>
       <c r="B151" t="n">
         <v>57975</v>
@@ -17421,7 +17407,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17430,13 +17416,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>635169</v>
+        <v>635186</v>
       </c>
       <c r="R151" t="n">
-        <v>7292222</v>
+        <v>7292228</v>
       </c>
       <c r="S151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17465,7 +17451,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17475,12 +17461,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17511,7 +17497,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135331437</v>
+        <v>135331436</v>
       </c>
       <c r="B152" t="n">
         <v>57975</v>
@@ -17542,7 +17528,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17551,13 +17537,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>635171</v>
+        <v>635169</v>
       </c>
       <c r="R152" t="n">
-        <v>7292250</v>
+        <v>7292222</v>
       </c>
       <c r="S152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17586,7 +17572,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17596,12 +17582,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17632,7 +17618,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135331438</v>
+        <v>135331437</v>
       </c>
       <c r="B153" t="n">
         <v>57975</v>
@@ -17663,7 +17649,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17672,10 +17658,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>635120</v>
+        <v>635171</v>
       </c>
       <c r="R153" t="n">
-        <v>7292313</v>
+        <v>7292250</v>
       </c>
       <c r="S153" t="n">
         <v>3</v>
@@ -17707,7 +17693,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17717,12 +17703,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17753,7 +17739,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135331441</v>
+        <v>135331438</v>
       </c>
       <c r="B154" t="n">
         <v>57975</v>
@@ -17784,7 +17770,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17793,10 +17779,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>634866</v>
+        <v>635120</v>
       </c>
       <c r="R154" t="n">
-        <v>7292532</v>
+        <v>7292313</v>
       </c>
       <c r="S154" t="n">
         <v>3</v>
@@ -17828,7 +17814,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17838,12 +17824,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17874,48 +17860,53 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135325225</v>
+        <v>135331441</v>
       </c>
       <c r="B155" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Maskaure maddagielas s, Pi lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>634940</v>
+        <v>634866</v>
       </c>
       <c r="R155" t="n">
-        <v>7292440</v>
+        <v>7292532</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17944,7 +17935,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17954,7 +17945,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17969,12 +17965,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -17985,7 +17981,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135325229</v>
+        <v>135325225</v>
       </c>
       <c r="B156" t="n">
         <v>99112</v>
@@ -18020,13 +18016,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>634927</v>
+        <v>634940</v>
       </c>
       <c r="R156" t="n">
-        <v>7292364</v>
+        <v>7292440</v>
       </c>
       <c r="S156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18055,7 +18051,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18065,7 +18061,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18096,7 +18092,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135325235</v>
+        <v>135325229</v>
       </c>
       <c r="B157" t="n">
         <v>99112</v>
@@ -18131,13 +18127,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>634815</v>
+        <v>634927</v>
       </c>
       <c r="R157" t="n">
-        <v>7292218</v>
+        <v>7292364</v>
       </c>
       <c r="S157" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18166,7 +18162,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18176,7 +18172,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18207,7 +18203,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135325238</v>
+        <v>135325235</v>
       </c>
       <c r="B158" t="n">
         <v>99112</v>
@@ -18242,13 +18238,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>634769</v>
+        <v>634815</v>
       </c>
       <c r="R158" t="n">
-        <v>7292359</v>
+        <v>7292218</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18277,7 +18273,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18287,7 +18283,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18318,7 +18314,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135325240</v>
+        <v>135325238</v>
       </c>
       <c r="B159" t="n">
         <v>99112</v>
@@ -18353,13 +18349,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>634715</v>
+        <v>634769</v>
       </c>
       <c r="R159" t="n">
-        <v>7292480</v>
+        <v>7292359</v>
       </c>
       <c r="S159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18388,7 +18384,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18398,7 +18394,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18429,7 +18425,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135332486</v>
+        <v>135325240</v>
       </c>
       <c r="B160" t="n">
         <v>99112</v>
@@ -18460,17 +18456,17 @@
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>635110</v>
+        <v>634715</v>
       </c>
       <c r="R160" t="n">
-        <v>7292382</v>
+        <v>7292480</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18499,7 +18495,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18509,7 +18505,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18524,12 +18520,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -18540,10 +18536,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135325230</v>
+        <v>135332486</v>
       </c>
       <c r="B161" t="n">
-        <v>99217</v>
+        <v>99112</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18551,34 +18547,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>634927</v>
+        <v>635110</v>
       </c>
       <c r="R161" t="n">
-        <v>7292364</v>
+        <v>7292382</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18610,7 +18606,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18620,7 +18616,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18635,12 +18631,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -18651,7 +18647,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135325231</v>
+        <v>135325230</v>
       </c>
       <c r="B162" t="n">
         <v>99217</v>
@@ -18686,13 +18682,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>634915</v>
+        <v>634927</v>
       </c>
       <c r="R162" t="n">
-        <v>7292330</v>
+        <v>7292364</v>
       </c>
       <c r="S162" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18721,7 +18717,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18731,7 +18727,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18762,7 +18758,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135325233</v>
+        <v>135325231</v>
       </c>
       <c r="B163" t="n">
         <v>99217</v>
@@ -18797,13 +18793,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>634889</v>
+        <v>634915</v>
       </c>
       <c r="R163" t="n">
-        <v>7292260</v>
+        <v>7292330</v>
       </c>
       <c r="S163" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18832,7 +18828,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18842,7 +18838,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18873,7 +18869,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135325236</v>
+        <v>135325233</v>
       </c>
       <c r="B164" t="n">
         <v>99217</v>
@@ -18908,10 +18904,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>634780</v>
+        <v>634889</v>
       </c>
       <c r="R164" t="n">
-        <v>7292300</v>
+        <v>7292260</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18943,7 +18939,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18953,7 +18949,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18984,7 +18980,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135325241</v>
+        <v>135325236</v>
       </c>
       <c r="B165" t="n">
         <v>99217</v>
@@ -19019,10 +19015,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>634798</v>
+        <v>634780</v>
       </c>
       <c r="R165" t="n">
-        <v>7292531</v>
+        <v>7292300</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -19054,7 +19050,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19064,7 +19060,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19095,7 +19091,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135325245</v>
+        <v>135325241</v>
       </c>
       <c r="B166" t="n">
         <v>99217</v>
@@ -19130,10 +19126,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>634901</v>
+        <v>634798</v>
       </c>
       <c r="R166" t="n">
-        <v>7292553</v>
+        <v>7292531</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -19165,7 +19161,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19175,7 +19171,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19206,7 +19202,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135332523</v>
+        <v>135325245</v>
       </c>
       <c r="B167" t="n">
         <v>99217</v>
@@ -19237,17 +19233,17 @@
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>634953</v>
+        <v>634901</v>
       </c>
       <c r="R167" t="n">
-        <v>7292430</v>
+        <v>7292553</v>
       </c>
       <c r="S167" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19276,7 +19272,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19286,7 +19282,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19301,12 +19297,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -19317,48 +19313,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135325214</v>
+        <v>135332523</v>
       </c>
       <c r="B168" t="n">
-        <v>92201</v>
+        <v>99217</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>67</v>
+        <v>221952</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>634967</v>
+        <v>634953</v>
       </c>
       <c r="R168" t="n">
-        <v>7292615</v>
+        <v>7292430</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19387,7 +19383,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19397,7 +19393,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19412,12 +19408,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -19428,32 +19424,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135325215</v>
+        <v>135325214</v>
       </c>
       <c r="B169" t="n">
-        <v>92245</v>
+        <v>92201</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19463,13 +19459,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>634969</v>
+        <v>634967</v>
       </c>
       <c r="R169" t="n">
-        <v>7292609</v>
+        <v>7292615</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19498,7 +19494,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19508,7 +19504,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19539,10 +19535,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>135332481</v>
+        <v>135325215</v>
       </c>
       <c r="B170" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19550,34 +19546,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>634879</v>
+        <v>634969</v>
       </c>
       <c r="R170" t="n">
-        <v>7292687</v>
+        <v>7292609</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19609,7 +19605,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19619,7 +19615,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19634,12 +19630,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -19650,10 +19646,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>135330164</v>
+        <v>135332481</v>
       </c>
       <c r="B171" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19661,34 +19657,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634732</v>
+        <v>634879</v>
       </c>
       <c r="R171" t="n">
-        <v>7292789</v>
+        <v>7292687</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19720,7 +19716,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19730,7 +19726,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19745,12 +19741,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -19761,7 +19757,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>135332017</v>
+        <v>135330164</v>
       </c>
       <c r="B172" t="n">
         <v>91970</v>
@@ -19792,14 +19788,14 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>634721</v>
+        <v>634732</v>
       </c>
       <c r="R172" t="n">
-        <v>7292806</v>
+        <v>7292789</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19831,7 +19827,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19841,7 +19837,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19856,12 +19852,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -19872,10 +19868,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>135325212</v>
+        <v>135332017</v>
       </c>
       <c r="B173" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19883,37 +19879,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>634893</v>
+        <v>634721</v>
       </c>
       <c r="R173" t="n">
-        <v>7292634</v>
+        <v>7292806</v>
       </c>
       <c r="S173" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19942,7 +19938,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19952,7 +19948,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19967,12 +19963,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -19983,7 +19979,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>135325250</v>
+        <v>135325212</v>
       </c>
       <c r="B174" t="n">
         <v>91974</v>
@@ -20018,13 +20014,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>634977</v>
+        <v>634893</v>
       </c>
       <c r="R174" t="n">
-        <v>7292676</v>
+        <v>7292634</v>
       </c>
       <c r="S174" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20053,7 +20049,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20063,7 +20059,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20094,32 +20090,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>135325210</v>
+        <v>135325250</v>
       </c>
       <c r="B175" t="n">
-        <v>92370</v>
+        <v>91974</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20129,13 +20125,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>634884</v>
+        <v>634977</v>
       </c>
       <c r="R175" t="n">
-        <v>7292692</v>
+        <v>7292676</v>
       </c>
       <c r="S175" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20164,7 +20160,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20174,12 +20170,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20210,10 +20201,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>135325202</v>
+        <v>135325210</v>
       </c>
       <c r="B176" t="n">
-        <v>91937</v>
+        <v>92370</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20221,21 +20212,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -20245,13 +20236,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>634834</v>
+        <v>634884</v>
       </c>
       <c r="R176" t="n">
-        <v>7292705</v>
+        <v>7292692</v>
       </c>
       <c r="S176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20280,7 +20271,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20290,7 +20281,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20321,7 +20317,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>135325205</v>
+        <v>135325202</v>
       </c>
       <c r="B177" t="n">
         <v>91937</v>
@@ -20356,13 +20352,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>634861</v>
+        <v>634834</v>
       </c>
       <c r="R177" t="n">
-        <v>7292707</v>
+        <v>7292705</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20391,7 +20387,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20401,7 +20397,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20432,7 +20428,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>135370468</v>
+        <v>135325205</v>
       </c>
       <c r="B178" t="n">
         <v>91937</v>
@@ -20463,17 +20459,17 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas N+S, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>634673</v>
+        <v>634861</v>
       </c>
       <c r="R178" t="n">
-        <v>7292744</v>
+        <v>7292707</v>
       </c>
       <c r="S178" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20502,7 +20498,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20512,12 +20508,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>På mindre, död gran.</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20532,12 +20523,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Linnea Ingelsbo</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -20548,48 +20539,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>135325196</v>
+        <v>135370468</v>
       </c>
       <c r="B179" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Maskaure Maddagielas N+S, Pi lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>634757</v>
+        <v>634673</v>
       </c>
       <c r="R179" t="n">
-        <v>7292709</v>
+        <v>7292744</v>
       </c>
       <c r="S179" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20618,7 +20609,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20628,7 +20619,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>På mindre, död gran.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20643,12 +20639,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Maja Josefsson, Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -20659,7 +20655,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>135325199</v>
+        <v>135325196</v>
       </c>
       <c r="B180" t="n">
         <v>79373</v>
@@ -20694,10 +20690,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>634802</v>
+        <v>634757</v>
       </c>
       <c r="R180" t="n">
-        <v>7292691</v>
+        <v>7292709</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20729,7 +20725,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20739,7 +20735,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20770,7 +20766,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>135325209</v>
+        <v>135325199</v>
       </c>
       <c r="B181" t="n">
         <v>79373</v>
@@ -20805,10 +20801,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>634882</v>
+        <v>634802</v>
       </c>
       <c r="R181" t="n">
-        <v>7292677</v>
+        <v>7292691</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -20840,7 +20836,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20850,7 +20846,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20881,7 +20877,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>135325251</v>
+        <v>135325209</v>
       </c>
       <c r="B182" t="n">
         <v>79373</v>
@@ -20916,13 +20912,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>634958</v>
+        <v>634882</v>
       </c>
       <c r="R182" t="n">
-        <v>7292671</v>
+        <v>7292677</v>
       </c>
       <c r="S182" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20951,7 +20947,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20961,7 +20957,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20992,7 +20988,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>135330165</v>
+        <v>135325251</v>
       </c>
       <c r="B183" t="n">
         <v>79373</v>
@@ -21023,17 +21019,17 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>634886</v>
+        <v>634958</v>
       </c>
       <c r="R183" t="n">
-        <v>7292680</v>
+        <v>7292671</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21062,7 +21058,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -21072,7 +21068,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21087,12 +21083,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -21103,45 +21099,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>135325211</v>
+        <v>135330165</v>
       </c>
       <c r="B184" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>634892</v>
+        <v>634886</v>
       </c>
       <c r="R184" t="n">
-        <v>7292656</v>
+        <v>7292680</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21173,7 +21169,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21183,7 +21179,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21198,12 +21194,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -21214,10 +21210,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>135370471</v>
+        <v>135325211</v>
       </c>
       <c r="B185" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21225,37 +21221,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas N+S, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>634688</v>
+        <v>634892</v>
       </c>
       <c r="R185" t="n">
-        <v>7292863</v>
+        <v>7292656</v>
       </c>
       <c r="S185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21284,7 +21280,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21294,12 +21290,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>På rester av tall.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21314,12 +21305,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Linnea Ingelsbo</t>
+          <t>Pia Edfors, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -21330,48 +21321,48 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>135513446</v>
+        <v>135370471</v>
       </c>
       <c r="B186" t="n">
-        <v>80492</v>
+        <v>79992</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas N+S, Pi lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>634713</v>
+        <v>634688</v>
       </c>
       <c r="R186" t="n">
-        <v>7292779</v>
+        <v>7292863</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21400,7 +21391,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21410,7 +21401,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>På rester av tall.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21425,59 +21421,58 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY186" t="inlineStr"/>
+          <t>Maja Josefsson, Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>135250794</v>
+        <v>135513446</v>
       </c>
       <c r="B187" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Maddávrrie, Maddávrrie, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>634837</v>
+        <v>634713</v>
       </c>
       <c r="R187" t="n">
         <v>7292779</v>
@@ -21507,17 +21502,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gran.</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21532,19 +21532,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>135331406</v>
+        <v>135250794</v>
       </c>
       <c r="B188" t="n">
         <v>57975</v>
@@ -21580,17 +21580,17 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Maskaure maddagielas s, Pi lm</t>
+          <t>Maddávrrie, Maddávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>634875</v>
+        <v>634837</v>
       </c>
       <c r="R188" t="n">
-        <v>7292694</v>
+        <v>7292779</v>
       </c>
       <c r="S188" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21614,27 +21614,17 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack i gran.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21649,26 +21639,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY188" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>135325213</v>
+        <v>135331406</v>
       </c>
       <c r="B189" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21676,37 +21662,42 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas, Pi lm</t>
+          <t>Maskaure maddagielas s, Pi lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>634950</v>
+        <v>634875</v>
       </c>
       <c r="R189" t="n">
-        <v>7292624</v>
+        <v>7292694</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21735,7 +21726,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21745,7 +21736,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21760,12 +21756,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Pia Edfors, Sofia Fransén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -21776,32 +21772,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>135325195</v>
+        <v>135325213</v>
       </c>
       <c r="B190" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21811,10 +21807,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>634716</v>
+        <v>634950</v>
       </c>
       <c r="R190" t="n">
-        <v>7292691</v>
+        <v>7292624</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21846,7 +21842,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21856,7 +21852,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21887,10 +21883,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135325197</v>
+        <v>135325195</v>
       </c>
       <c r="B191" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21898,21 +21894,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21922,10 +21918,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>634757</v>
+        <v>634716</v>
       </c>
       <c r="R191" t="n">
-        <v>7292709</v>
+        <v>7292691</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -21957,7 +21953,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21967,7 +21963,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21998,7 +21994,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135325201</v>
+        <v>135325197</v>
       </c>
       <c r="B192" t="n">
         <v>99099</v>
@@ -22033,13 +22029,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>634821</v>
+        <v>634757</v>
       </c>
       <c r="R192" t="n">
-        <v>7292707</v>
+        <v>7292709</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22068,7 +22064,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22078,7 +22074,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22109,7 +22105,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>135325255</v>
+        <v>135325201</v>
       </c>
       <c r="B193" t="n">
         <v>99099</v>
@@ -22144,13 +22140,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>634849</v>
+        <v>634821</v>
       </c>
       <c r="R193" t="n">
-        <v>7292752</v>
+        <v>7292707</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22179,7 +22175,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22189,7 +22185,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22220,10 +22216,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135325217</v>
+        <v>135325255</v>
       </c>
       <c r="B194" t="n">
-        <v>106309</v>
+        <v>99099</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22231,21 +22227,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22255,13 +22251,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>634990</v>
+        <v>634849</v>
       </c>
       <c r="R194" t="n">
-        <v>7292586</v>
+        <v>7292752</v>
       </c>
       <c r="S194" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22290,7 +22286,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22300,7 +22296,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22331,10 +22327,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135325216</v>
+        <v>135325217</v>
       </c>
       <c r="B195" t="n">
-        <v>98066</v>
+        <v>106309</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22342,21 +22338,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22366,13 +22362,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>634997</v>
+        <v>634990</v>
       </c>
       <c r="R195" t="n">
-        <v>7292604</v>
+        <v>7292586</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22401,7 +22397,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22411,7 +22407,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22442,10 +22438,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135325203</v>
+        <v>135325216</v>
       </c>
       <c r="B196" t="n">
-        <v>98060</v>
+        <v>98066</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22453,16 +22449,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -22477,13 +22473,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>634855</v>
+        <v>634997</v>
       </c>
       <c r="R196" t="n">
-        <v>7292707</v>
+        <v>7292604</v>
       </c>
       <c r="S196" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22512,7 +22508,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22522,7 +22518,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22553,10 +22549,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135513308</v>
+        <v>135325203</v>
       </c>
       <c r="B197" t="n">
-        <v>98063</v>
+        <v>98060</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22564,16 +22560,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -22584,17 +22580,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>634820</v>
+        <v>634855</v>
       </c>
       <c r="R197" t="n">
-        <v>7292749</v>
+        <v>7292707</v>
       </c>
       <c r="S197" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22623,7 +22619,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22633,7 +22629,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22648,15 +22644,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY197" t="inlineStr"/>
+          <t>Pia Edfors, Sofia Fransén</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -16839,9 +16839,12 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
@@ -16899,6 +16902,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16913,7 +16917,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -21466,9 +21474,12 @@
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas N, Pi lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
@@ -21526,6 +21537,7 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -21540,7 +21552,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY204"/>
+  <dimension ref="A1:AZ204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325439</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325440</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325441</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330768</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330769</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320953</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320956</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320961</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330764</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330766</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320955</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330761</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2453,6 +2533,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325438</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,6 +2649,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330767</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2675,6 +2765,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330762</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2786,6 +2881,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333679</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +2997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320945</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3009,6 +3114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320946</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3120,6 +3230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320931</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3231,6 +3346,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320949</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3342,6 +3462,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325417</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3453,6 +3578,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330783</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3564,6 +3694,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330803</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3681,6 +3816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333677</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3792,6 +3932,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320970</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3903,6 +4048,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320924</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4014,6 +4164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330770</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4125,6 +4280,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320938</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4236,6 +4396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331602</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4353,6 +4518,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135250417</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4464,6 +4634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325436</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4575,6 +4750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330776</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4692,6 +4872,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135250442</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4803,6 +4988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320936</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4914,6 +5104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320950</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5025,6 +5220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325189</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5136,6 +5336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325256</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5247,6 +5452,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325414</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5358,6 +5568,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325415</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5469,6 +5684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325416</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5580,6 +5800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325419</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5691,6 +5916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325422</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5802,6 +6032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325424</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5913,6 +6148,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325426</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6024,6 +6264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325427</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6135,6 +6380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325429</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6246,6 +6496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325430</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6357,6 +6612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325432</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6468,6 +6728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325434</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6579,6 +6844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325437</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6690,6 +6960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325445</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6801,6 +7076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330771</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6912,6 +7192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330774</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7023,6 +7308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330780</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7134,6 +7424,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330782</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7250,6 +7545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330784</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7361,6 +7661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330787</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7472,6 +7777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330789</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7583,6 +7893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330796</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7694,6 +8009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330804</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7810,6 +8130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370463</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7926,6 +8251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370473</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8037,6 +8367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320965</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8148,6 +8483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320968</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8259,6 +8599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320927</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8370,6 +8715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320930</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8481,6 +8831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320937</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8592,6 +8947,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320947</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8703,6 +9063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330778</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8814,6 +9179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330786</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8925,6 +9295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330792</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9036,6 +9411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330797</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9147,6 +9527,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330805</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9258,6 +9643,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333681</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9369,6 +9759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333682</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9480,6 +9875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333686</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9591,6 +9991,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333694</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9707,6 +10112,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370467</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9818,6 +10228,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320932</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9929,6 +10344,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320940</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10040,6 +10460,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320951</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10151,6 +10576,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320967</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10262,6 +10692,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325190</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10373,6 +10808,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325193</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10484,6 +10924,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325428</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10595,6 +11040,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333698</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10711,6 +11161,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370459</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10822,6 +11277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325418</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10933,6 +11393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320925</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11044,6 +11509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320943</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11155,6 +11625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325447</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11266,6 +11741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333697</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11377,6 +11857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320929</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11488,6 +11973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320969</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11604,6 +12094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325435</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11720,6 +12215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325443</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11836,6 +12336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330760</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11952,6 +12457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320966</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12068,6 +12578,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325420</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12184,6 +12699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325423</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12300,6 +12820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330773</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12414,6 +12939,11 @@
       <c r="AY106" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330800</t>
         </is>
       </c>
     </row>
@@ -12536,6 +13066,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330801</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12652,6 +13187,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370457</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12768,6 +13308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370460</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12884,6 +13429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370465</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13000,6 +13550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330757</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13132,6 +13687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333700</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13243,6 +13803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320952</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13359,6 +13924,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330788</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13475,6 +14045,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325433</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13587,6 +14162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330798</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13699,6 +14279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330799</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13810,6 +14395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333689</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13921,6 +14511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330754</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14032,6 +14627,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333696</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14143,6 +14743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330791</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14254,6 +14859,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320971</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14365,6 +14975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325192</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14476,6 +15091,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330777</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14587,6 +15207,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330779</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14698,6 +15323,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333683</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14809,6 +15439,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333685</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14920,6 +15555,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333690</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15036,6 +15676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370462</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15147,6 +15792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333695</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15258,6 +15908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325444</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15369,6 +16024,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320941</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15480,6 +16140,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330781</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15586,6 +16251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320944</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15697,6 +16367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325242</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15808,6 +16483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325222</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15919,6 +16599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325246</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16030,6 +16715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325243</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16141,6 +16831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325224</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16252,6 +16947,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325228</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16363,6 +17063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325232</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16474,6 +17179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332487</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16585,6 +17295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332483</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16696,6 +17411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325220</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16805,6 +17525,11 @@
       <c r="AY145" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332018</t>
         </is>
       </c>
     </row>
@@ -16922,6 +17647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513719</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17033,6 +17763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325219</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17144,6 +17879,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325234</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17260,6 +18000,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325223</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17381,6 +18126,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331408</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17502,6 +18252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331435</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17623,6 +18378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331436</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17744,6 +18504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331437</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17865,6 +18630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331438</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17986,6 +18756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331441</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18097,6 +18872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325225</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18208,6 +18988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325229</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18319,6 +19104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325235</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18430,6 +19220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325238</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18541,6 +19336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325240</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18652,6 +19452,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332486</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18763,6 +19568,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325230</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18874,6 +19684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325231</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18985,6 +19800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325233</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19096,6 +19916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325236</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19207,6 +20032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325241</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19318,6 +20148,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325245</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19429,6 +20264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332523</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19540,6 +20380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325214</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19651,6 +20496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325215</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19762,6 +20612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332481</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19873,6 +20728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330164</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19984,6 +20844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332017</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20095,6 +20960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325212</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20206,6 +21076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325250</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20322,6 +21197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325210</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20433,6 +21313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325202</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20544,6 +21429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325205</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20660,6 +21550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370468</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20771,6 +21666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325196</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20882,6 +21782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325199</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20993,6 +21898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325209</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21104,6 +22014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325251</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21215,6 +22130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330165</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21326,6 +22246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325211</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21440,6 +22365,11 @@
       <c r="AY186" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370471</t>
         </is>
       </c>
     </row>
@@ -21557,6 +22487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513446</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21664,6 +22599,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135250794</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21785,6 +22725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331406</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21896,6 +22841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325213</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22007,6 +22957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325195</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22118,6 +23073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325197</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22229,6 +23189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325201</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22340,6 +23305,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325255</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22451,6 +23421,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325217</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22562,6 +23537,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325216</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22673,6 +23653,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325203</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22784,6 +23769,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325194</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22895,6 +23885,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325198</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23006,6 +24001,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325206</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23117,6 +24117,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325207</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23228,6 +24233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325249</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23339,6 +24349,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325253</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23450,8 +24465,218 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -17102,7 +17102,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
@@ -17218,7 +17218,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
@@ -19375,7 +19375,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
@@ -20187,7 +20187,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
@@ -20535,7 +20535,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas N, Pi lm</t>
         </is>
       </c>
       <c r="Q171" t="n">

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135320963</v>
       </c>
       <c r="B2" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135320962</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135320958</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135325439</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135325440</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135325441</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135330768</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135330769</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135320953</v>
       </c>
       <c r="B10" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135320956</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135320961</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135330764</v>
       </c>
       <c r="B13" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135330766</v>
       </c>
       <c r="B14" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135320955</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135330761</v>
       </c>
       <c r="B16" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135325438</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>135330767</v>
       </c>
       <c r="B18" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135330762</v>
       </c>
       <c r="B19" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>135320945</v>
       </c>
       <c r="B21" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135320946</v>
       </c>
       <c r="B22" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135320931</v>
       </c>
       <c r="B23" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>135320949</v>
       </c>
       <c r="B24" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>135325417</v>
       </c>
       <c r="B25" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135330783</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135330803</v>
       </c>
       <c r="B27" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92689</v>
+        <v>92731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>135320970</v>
       </c>
       <c r="B29" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>135320924</v>
       </c>
       <c r="B30" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>135330770</v>
       </c>
       <c r="B31" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>135320938</v>
       </c>
       <c r="B32" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>135331602</v>
       </c>
       <c r="B33" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>135250417</v>
       </c>
       <c r="B34" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>135325436</v>
       </c>
       <c r="B35" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135330776</v>
       </c>
       <c r="B36" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>135250442</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>135320936</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>135320950</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>135325189</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135325256</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>135325414</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>135325415</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>135325416</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>135325419</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>135325422</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>135325424</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>135325426</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>135325427</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>135325429</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135325430</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>135325432</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>135325434</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>135325437</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>135325445</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>135330771</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135330774</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>135330780</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>135330782</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>135330784</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>135330787</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>135330789</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>135330796</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>135330804</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>135370463</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>135370473</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>135320965</v>
       </c>
       <c r="B67" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>135320968</v>
       </c>
       <c r="B68" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>135320927</v>
       </c>
       <c r="B69" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>135320930</v>
       </c>
       <c r="B70" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135320937</v>
       </c>
       <c r="B71" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>135320947</v>
       </c>
       <c r="B72" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>135330778</v>
       </c>
       <c r="B73" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>135330786</v>
       </c>
       <c r="B74" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>135330792</v>
       </c>
       <c r="B75" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>135330797</v>
       </c>
       <c r="B76" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>135330805</v>
       </c>
       <c r="B77" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>135370467</v>
       </c>
       <c r="B82" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>135320932</v>
       </c>
       <c r="B83" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>135320940</v>
       </c>
       <c r="B84" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>135320951</v>
       </c>
       <c r="B85" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>135320967</v>
       </c>
       <c r="B86" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>135325190</v>
       </c>
       <c r="B87" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>135325193</v>
       </c>
       <c r="B88" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>135325428</v>
       </c>
       <c r="B89" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>135370459</v>
       </c>
       <c r="B91" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135325418</v>
       </c>
       <c r="B92" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135320925</v>
       </c>
       <c r="B93" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>135320943</v>
       </c>
       <c r="B94" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>135325447</v>
       </c>
       <c r="B95" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>135320929</v>
       </c>
       <c r="B97" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>135320969</v>
       </c>
       <c r="B98" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>135325435</v>
       </c>
       <c r="B99" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>135325443</v>
       </c>
       <c r="B100" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>135330760</v>
       </c>
       <c r="B101" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>135320966</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>135325420</v>
       </c>
       <c r="B103" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>135325423</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>135330773</v>
       </c>
       <c r="B105" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>135330800</v>
       </c>
       <c r="B106" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135330801</v>
       </c>
       <c r="B107" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>135370457</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>135370460</v>
       </c>
       <c r="B109" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>135370465</v>
       </c>
       <c r="B110" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>135330757</v>
       </c>
       <c r="B111" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>135333700</v>
       </c>
       <c r="B112" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>135320952</v>
       </c>
       <c r="B113" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>135330788</v>
       </c>
       <c r="B114" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>135325433</v>
       </c>
       <c r="B115" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>135330798</v>
       </c>
       <c r="B116" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>135330799</v>
       </c>
       <c r="B117" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>135333689</v>
       </c>
       <c r="B118" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>135330754</v>
       </c>
       <c r="B119" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>135330791</v>
       </c>
       <c r="B121" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>135320971</v>
       </c>
       <c r="B122" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>135325192</v>
       </c>
       <c r="B123" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>135330777</v>
       </c>
       <c r="B124" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>135330779</v>
       </c>
       <c r="B125" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>135370462</v>
       </c>
       <c r="B129" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>135325444</v>
       </c>
       <c r="B131" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>135320941</v>
       </c>
       <c r="B132" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>135330781</v>
       </c>
       <c r="B133" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>135320944</v>
       </c>
       <c r="B134" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>135325242</v>
       </c>
       <c r="B135" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>135325222</v>
       </c>
       <c r="B136" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135325246</v>
       </c>
       <c r="B137" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>135325243</v>
       </c>
       <c r="B138" t="n">
-        <v>92188</v>
+        <v>92230</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>135325224</v>
       </c>
       <c r="B139" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>135325228</v>
       </c>
       <c r="B140" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>135325232</v>
       </c>
       <c r="B141" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>135332487</v>
       </c>
       <c r="B142" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>135332483</v>
       </c>
       <c r="B143" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>135325220</v>
       </c>
       <c r="B144" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>135332018</v>
       </c>
       <c r="B145" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>135513719</v>
       </c>
       <c r="B146" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>135325219</v>
       </c>
       <c r="B147" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>135325234</v>
       </c>
       <c r="B148" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>135325223</v>
       </c>
       <c r="B149" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>135331408</v>
       </c>
       <c r="B150" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>135331435</v>
       </c>
       <c r="B151" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>135331436</v>
       </c>
       <c r="B152" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>135331437</v>
       </c>
       <c r="B153" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>135331438</v>
       </c>
       <c r="B154" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>135331441</v>
       </c>
       <c r="B155" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>135325225</v>
       </c>
       <c r="B156" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>135325229</v>
       </c>
       <c r="B157" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>135325235</v>
       </c>
       <c r="B158" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>135325238</v>
       </c>
       <c r="B159" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>135325240</v>
       </c>
       <c r="B160" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>135332486</v>
       </c>
       <c r="B161" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>135325230</v>
       </c>
       <c r="B162" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>135325231</v>
       </c>
       <c r="B163" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>135325233</v>
       </c>
       <c r="B164" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>135325236</v>
       </c>
       <c r="B165" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>135325241</v>
       </c>
       <c r="B166" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>135325245</v>
       </c>
       <c r="B167" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>135332523</v>
       </c>
       <c r="B168" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>135325214</v>
       </c>
       <c r="B169" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>135325215</v>
       </c>
       <c r="B170" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>135332481</v>
       </c>
       <c r="B171" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>135330164</v>
       </c>
       <c r="B172" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>135332017</v>
       </c>
       <c r="B173" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>135325212</v>
       </c>
       <c r="B174" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>135325250</v>
       </c>
       <c r="B175" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>135325210</v>
       </c>
       <c r="B176" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>135325202</v>
       </c>
       <c r="B177" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>135325205</v>
       </c>
       <c r="B178" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>135370468</v>
       </c>
       <c r="B179" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>135325196</v>
       </c>
       <c r="B180" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>135325199</v>
       </c>
       <c r="B181" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>135325209</v>
       </c>
       <c r="B182" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>135325251</v>
       </c>
       <c r="B183" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>135330165</v>
       </c>
       <c r="B184" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>135325211</v>
       </c>
       <c r="B185" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>135370471</v>
       </c>
       <c r="B186" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>135513446</v>
       </c>
       <c r="B187" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>135250794</v>
       </c>
       <c r="B188" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>135331406</v>
       </c>
       <c r="B189" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>135325213</v>
       </c>
       <c r="B190" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>135325195</v>
       </c>
       <c r="B191" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>135325197</v>
       </c>
       <c r="B192" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>135325201</v>
       </c>
       <c r="B193" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>135325255</v>
       </c>
       <c r="B194" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>135325217</v>
       </c>
       <c r="B195" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>135325216</v>
       </c>
       <c r="B196" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>135325203</v>
       </c>
       <c r="B197" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>135325194</v>
       </c>
       <c r="B198" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>135325198</v>
       </c>
       <c r="B199" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>135325206</v>
       </c>
       <c r="B200" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>135325207</v>
       </c>
       <c r="B201" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>135325249</v>
       </c>
       <c r="B202" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>135325253</v>
       </c>
       <c r="B203" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>135325254</v>
       </c>
       <c r="B204" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135320963</v>
       </c>
       <c r="B2" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135320962</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135320958</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135325439</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135325440</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135325441</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135330768</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135330769</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135320953</v>
       </c>
       <c r="B10" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135320956</v>
       </c>
       <c r="B11" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135320961</v>
       </c>
       <c r="B12" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135330764</v>
       </c>
       <c r="B13" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135330766</v>
       </c>
       <c r="B14" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135320955</v>
       </c>
       <c r="B15" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135330761</v>
       </c>
       <c r="B16" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135330762</v>
       </c>
       <c r="B19" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>135320945</v>
       </c>
       <c r="B21" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>135320946</v>
       </c>
       <c r="B22" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135320931</v>
       </c>
       <c r="B23" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>135320949</v>
       </c>
       <c r="B24" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>135325417</v>
       </c>
       <c r="B25" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135330783</v>
       </c>
       <c r="B26" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135330803</v>
       </c>
       <c r="B27" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92731</v>
+        <v>92758</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>135320970</v>
       </c>
       <c r="B29" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>135320924</v>
       </c>
       <c r="B30" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>135330770</v>
       </c>
       <c r="B31" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>135320938</v>
       </c>
       <c r="B32" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>135331602</v>
       </c>
       <c r="B33" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>135250417</v>
       </c>
       <c r="B34" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>135325436</v>
       </c>
       <c r="B35" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135330776</v>
       </c>
       <c r="B36" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>135250442</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>135320936</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>135320950</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>135325189</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135325256</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>135325414</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>135325415</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>135325416</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>135325419</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>135325422</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>135325424</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>135325426</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>135325427</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>135325429</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135325430</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>135325432</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>135325434</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>135325437</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>135325445</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>135330771</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135330774</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>135330780</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>135330782</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>135330784</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>135330787</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>135330789</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>135330796</v>
       </c>
       <c r="B63" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>135330804</v>
       </c>
       <c r="B64" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>135370463</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>135370473</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>135320965</v>
       </c>
       <c r="B67" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>135320968</v>
       </c>
       <c r="B68" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>135320927</v>
       </c>
       <c r="B69" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>135320930</v>
       </c>
       <c r="B70" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135320937</v>
       </c>
       <c r="B71" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>135320947</v>
       </c>
       <c r="B72" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>135330778</v>
       </c>
       <c r="B73" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>135330786</v>
       </c>
       <c r="B74" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>135330792</v>
       </c>
       <c r="B75" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>135330797</v>
       </c>
       <c r="B76" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>135330805</v>
       </c>
       <c r="B77" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>135370467</v>
       </c>
       <c r="B82" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>135320932</v>
       </c>
       <c r="B83" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>135320940</v>
       </c>
       <c r="B84" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>135320951</v>
       </c>
       <c r="B85" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>135320967</v>
       </c>
       <c r="B86" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>135325190</v>
       </c>
       <c r="B87" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>135325193</v>
       </c>
       <c r="B88" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>135325428</v>
       </c>
       <c r="B89" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>135370459</v>
       </c>
       <c r="B91" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135325418</v>
       </c>
       <c r="B92" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135320925</v>
       </c>
       <c r="B93" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>135320943</v>
       </c>
       <c r="B94" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>135325447</v>
       </c>
       <c r="B95" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>135320929</v>
       </c>
       <c r="B97" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>135320969</v>
       </c>
       <c r="B98" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>135330754</v>
       </c>
       <c r="B119" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>135330791</v>
       </c>
       <c r="B121" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>135320971</v>
       </c>
       <c r="B122" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>135325192</v>
       </c>
       <c r="B123" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>135330777</v>
       </c>
       <c r="B124" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>135330779</v>
       </c>
       <c r="B125" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>135370462</v>
       </c>
       <c r="B129" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>135325444</v>
       </c>
       <c r="B131" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>135320941</v>
       </c>
       <c r="B132" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>135330781</v>
       </c>
       <c r="B133" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>135320944</v>
       </c>
       <c r="B134" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>135325242</v>
       </c>
       <c r="B135" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>135325222</v>
       </c>
       <c r="B136" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135325246</v>
       </c>
       <c r="B137" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>135325243</v>
       </c>
       <c r="B138" t="n">
-        <v>92230</v>
+        <v>92257</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>135325224</v>
       </c>
       <c r="B139" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>135325228</v>
       </c>
       <c r="B140" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>135325232</v>
       </c>
       <c r="B141" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>135332487</v>
       </c>
       <c r="B142" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>135332483</v>
       </c>
       <c r="B143" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>135325220</v>
       </c>
       <c r="B144" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>135332018</v>
       </c>
       <c r="B145" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>135513719</v>
       </c>
       <c r="B146" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>135325219</v>
       </c>
       <c r="B147" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>135325234</v>
       </c>
       <c r="B148" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>135325225</v>
       </c>
       <c r="B156" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>135325229</v>
       </c>
       <c r="B157" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>135325235</v>
       </c>
       <c r="B158" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>135325238</v>
       </c>
       <c r="B159" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>135325240</v>
       </c>
       <c r="B160" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>135332486</v>
       </c>
       <c r="B161" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>135325230</v>
       </c>
       <c r="B162" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>135325231</v>
       </c>
       <c r="B163" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>135325233</v>
       </c>
       <c r="B164" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>135325236</v>
       </c>
       <c r="B165" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>135325241</v>
       </c>
       <c r="B166" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>135325245</v>
       </c>
       <c r="B167" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>135332523</v>
       </c>
       <c r="B168" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>135325214</v>
       </c>
       <c r="B169" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>135325215</v>
       </c>
       <c r="B170" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>135332481</v>
       </c>
       <c r="B171" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>135330164</v>
       </c>
       <c r="B172" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>135332017</v>
       </c>
       <c r="B173" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>135325212</v>
       </c>
       <c r="B174" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>135325250</v>
       </c>
       <c r="B175" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>135325210</v>
       </c>
       <c r="B176" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>135325202</v>
       </c>
       <c r="B177" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>135325205</v>
       </c>
       <c r="B178" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>135370468</v>
       </c>
       <c r="B179" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>135325196</v>
       </c>
       <c r="B180" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>135325199</v>
       </c>
       <c r="B181" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>135325209</v>
       </c>
       <c r="B182" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>135325251</v>
       </c>
       <c r="B183" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>135330165</v>
       </c>
       <c r="B184" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>135325211</v>
       </c>
       <c r="B185" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>135370471</v>
       </c>
       <c r="B186" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>135513446</v>
       </c>
       <c r="B187" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>135325195</v>
       </c>
       <c r="B191" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>135325197</v>
       </c>
       <c r="B192" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>135325201</v>
       </c>
       <c r="B193" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>135325255</v>
       </c>
       <c r="B194" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>135325217</v>
       </c>
       <c r="B195" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>135325216</v>
       </c>
       <c r="B196" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>135325203</v>
       </c>
       <c r="B197" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>135325194</v>
       </c>
       <c r="B198" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>135325198</v>
       </c>
       <c r="B199" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>135325206</v>
       </c>
       <c r="B200" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>135325207</v>
       </c>
       <c r="B201" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>135325249</v>
       </c>
       <c r="B202" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>135325253</v>
       </c>
       <c r="B203" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>135325254</v>
       </c>
       <c r="B204" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linnea Ingelsbo, Maja Josefsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135320962</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135330762</v>
       </c>
       <c r="B19" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>135320924</v>
       </c>
       <c r="B30" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>135330770</v>
       </c>
       <c r="B31" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>135250417</v>
       </c>
       <c r="B34" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>135325436</v>
       </c>
       <c r="B35" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135330776</v>
       </c>
       <c r="B36" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>135330754</v>
       </c>
       <c r="B119" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>135330791</v>
       </c>
       <c r="B121" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>135320971</v>
       </c>
       <c r="B122" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>135325192</v>
       </c>
       <c r="B123" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>135330777</v>
       </c>
       <c r="B124" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>135330779</v>
       </c>
       <c r="B125" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>135370462</v>
       </c>
       <c r="B129" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135325246</v>
       </c>
       <c r="B137" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>135325243</v>
       </c>
       <c r="B138" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>135325225</v>
       </c>
       <c r="B156" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>135325229</v>
       </c>
       <c r="B157" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>135325235</v>
       </c>
       <c r="B158" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>135325238</v>
       </c>
       <c r="B159" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>135325240</v>
       </c>
       <c r="B160" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>135332486</v>
       </c>
       <c r="B161" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>135325230</v>
       </c>
       <c r="B162" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>135325231</v>
       </c>
       <c r="B163" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>135325233</v>
       </c>
       <c r="B164" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>135325236</v>
       </c>
       <c r="B165" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>135325241</v>
       </c>
       <c r="B166" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>135325245</v>
       </c>
       <c r="B167" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>135332523</v>
       </c>
       <c r="B168" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>135325214</v>
       </c>
       <c r="B169" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>135325215</v>
       </c>
       <c r="B170" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>135330164</v>
       </c>
       <c r="B172" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>135332017</v>
       </c>
       <c r="B173" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>135325212</v>
       </c>
       <c r="B174" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>135325250</v>
       </c>
       <c r="B175" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>135325210</v>
       </c>
       <c r="B176" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>135325202</v>
       </c>
       <c r="B177" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>135325205</v>
       </c>
       <c r="B178" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>135370468</v>
       </c>
       <c r="B179" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>135325195</v>
       </c>
       <c r="B191" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>135325197</v>
       </c>
       <c r="B192" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>135325201</v>
       </c>
       <c r="B193" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>135325255</v>
       </c>
       <c r="B194" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>135325217</v>
       </c>
       <c r="B195" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>135325216</v>
       </c>
       <c r="B196" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>135325203</v>
       </c>
       <c r="B197" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>135325194</v>
       </c>
       <c r="B198" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>135325198</v>
       </c>
       <c r="B199" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>135325206</v>
       </c>
       <c r="B200" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>135325207</v>
       </c>
       <c r="B201" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>135325249</v>
       </c>
       <c r="B202" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>135325253</v>
       </c>
       <c r="B203" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>135325254</v>
       </c>
       <c r="B204" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92765</v>
+        <v>92780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>135333700</v>
       </c>
       <c r="B112" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>135333689</v>
       </c>
       <c r="B118" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>135332483</v>
       </c>
       <c r="B143" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>135513719</v>
       </c>
       <c r="B146" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>135332486</v>
       </c>
       <c r="B161" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>135332481</v>
       </c>
       <c r="B171" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>135513446</v>
       </c>
       <c r="B187" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>135332483</v>
       </c>
       <c r="B143" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>135513719</v>
       </c>
       <c r="B146" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>135332486</v>
       </c>
       <c r="B161" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>135332481</v>
       </c>
       <c r="B171" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>135513446</v>
       </c>
       <c r="B187" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>135333700</v>
       </c>
       <c r="B112" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>135333689</v>
       </c>
       <c r="B118" t="n">
-        <v>41612</v>
+        <v>41613</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>135333700</v>
       </c>
       <c r="B112" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>135333700</v>
       </c>
       <c r="B112" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78458</v>
+        <v>78459</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92790</v>
+        <v>92796</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99207</v>
+        <v>99218</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78459</v>
+        <v>78463</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas N, 68,3 ha artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>135333679</v>
       </c>
       <c r="B20" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>135333677</v>
       </c>
       <c r="B28" t="n">
-        <v>92796</v>
+        <v>92803</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135333681</v>
       </c>
       <c r="B78" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>135333682</v>
       </c>
       <c r="B79" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135333686</v>
       </c>
       <c r="B80" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>135333694</v>
       </c>
       <c r="B81" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135333698</v>
       </c>
       <c r="B90" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>135333697</v>
       </c>
       <c r="B96" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>135333700</v>
       </c>
       <c r="B112" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>135333689</v>
       </c>
       <c r="B118" t="n">
-        <v>41613</v>
+        <v>41618</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>135333696</v>
       </c>
       <c r="B120" t="n">
-        <v>99218</v>
+        <v>99231</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>135333683</v>
       </c>
       <c r="B126" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>135333685</v>
       </c>
       <c r="B127" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135333690</v>
       </c>
       <c r="B128" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>135333695</v>
       </c>
       <c r="B130" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
